--- a/ksoft/docs/records/Customer_Group_Records.xlsx
+++ b/ksoft/docs/records/Customer_Group_Records.xlsx
@@ -1345,13 +1345,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BEDF626-F2B9-4B1D-B80A-343A21656571}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA21E51-040E-42C4-B7F1-E4AD89B9CD3E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224F215A-9C17-4318-A7F2-F1FA55007A01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A3C491-AEC6-4F57-8079-CF6C1A7EB569}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C53E96A2-2B94-458E-9130-86A446858152}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813D1CC5-08A7-4895-97DB-A9398A1A13D0}"/>
 </file>
--- a/ksoft/docs/records/Customer_Group_Records.xlsx
+++ b/ksoft/docs/records/Customer_Group_Records.xlsx
@@ -1345,13 +1345,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA21E51-040E-42C4-B7F1-E4AD89B9CD3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BEDF626-F2B9-4B1D-B80A-343A21656571}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A3C491-AEC6-4F57-8079-CF6C1A7EB569}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224F215A-9C17-4318-A7F2-F1FA55007A01}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813D1CC5-08A7-4895-97DB-A9398A1A13D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C53E96A2-2B94-458E-9130-86A446858152}"/>
 </file>